--- a/F405_M3508_FOC/CAN_Control_Commands.xlsx
+++ b/F405_M3508_FOC/CAN_Control_Commands.xlsx
@@ -11,11 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="电流指令" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="速度指令" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="位置指令" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开环测试指令" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="USB文本命令" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'电流指令'!$A$1:$O$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'速度指令'!$A$1:$O$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'位置指令'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'开环测试指令'!$A$1:$R$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -437,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -525,6 +528,54 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>数据字节3~7暂时填 00</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>开环测试</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>数据字节0=20 进开环; 21 目标转速; 22 斜率(×1000); 23 电压上限(×1000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>开环转矩角/偏置</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24 转矩角 mrad; 25 观测角对照偏置 mrad</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>打点流</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>数据字节0=30, 值非0=开始 1kHz CSV 打点(走 USB 虚拟串口)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>USB 文本命令</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>同一根 USB 线上可直接敲 vf/stop/stream 等命令, 见 'USB文本命令' 页</t>
         </is>
       </c>
     </row>
@@ -2928,4 +2979,3281 @@
   <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>组号</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>子命令</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>含义</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>示例值</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>协议原始值</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>CAN ID</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>DLC</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节0</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节1</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节2</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节3</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节4</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节5</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节6</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>数据字节7</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>完整指令（单元格复制）</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>开环 V/F 开关</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0x91 8 20 00 01 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>非0=进入开环(驱动角用编码器电角度+转矩角); 0=退出并封驱动</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0x20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>开环 V/F 开关</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0x91 8 20 00 00 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>非0=进入开环(驱动角用编码器电角度+转矩角); 0=退出并封驱动</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x21</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>开环目标转速</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>rpm(电机侧)</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>800</v>
+      </c>
+      <c r="F4" t="n">
+        <v>800</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0x91 8 21 03 20 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>输出轴转速 = 该值/19; 内部斜坡到目标(0x26 设斜率)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x21</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>开环目标转速</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>rpm(电机侧)</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0x91 8 21 05 DC 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>输出轴转速 = 该值/19; 内部斜坡到目标(0x26 设斜率)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0x21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>开环目标转速</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>rpm(电机侧)</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>8</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0x91 8 21 09 C4 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>输出轴转速 = 该值/19; 内部斜坡到目标(0x26 设斜率)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0x22</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>V/F 电压/频率斜率</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>V/Hz</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>8</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>0x91 8 22 C3 50 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>原始值 = V/Hz×1000; 12V 母线建议 50~60</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0x22</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>V/F 电压/频率斜率</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>V/Hz</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>8</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0x91 8 22 EA 60 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>原始值 = V/Hz×1000; 12V 母线建议 50~60</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0x22</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>V/F 电压/频率斜率</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>V/Hz</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>80</v>
+      </c>
+      <c r="F9" t="n">
+        <v>80000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0x91 8 22 38 80 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>原始值 = V/Hz×1000; 12V 母线建议 50~60</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>V/F 电压上限</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>V(峰值相电压)</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6500</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2E</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>A0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0x91 8 23 2E A0 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>原始值 = V×1000; 12V 母线 SVPWM 线性区 ≈6.9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>V/F 电压上限</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>V(峰值相电压)</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>8</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>8D</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0x91 8 23 8D 80 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>原始值 = V×1000; 12V 母线 SVPWM 线性区 ≈6.9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>V/F 电压上限</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>V(峰值相电压)</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5500000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0x91 8 23 EC 60 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>原始值 = V×1000; 12V 母线 SVPWM 线性区 ≈6.9V</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>转矩角(磁场超前角)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1.5708</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15708</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3D</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>5C</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0x91 8 24 3D 5C 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>帧内原始值 = rad×10000(π/2=15708); 最大转矩/安培; 转向不对就发负值</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>转矩角(磁场超前角)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>-1.5708</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-15708</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>8</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0x91 8 24 C2 A4 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>帧内原始值 = rad×10000(π/2=15708); 最大转矩/安培; 转向不对就发负值</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>观测角对照偏置</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4613</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>8</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0x91 8 25 12 05 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>帧内原始值 = rad×10000; 只影响打点/显示的 err, 不动驱动; 默认 +0.4613</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>观测角对照偏置</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>8</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0x91 8 25 00 00 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>帧内原始值 = rad×10000; 只影响打点/显示的 err, 不动驱动; 默认 +0.4613</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>观测角对照偏置</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>rad</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.4613</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-4613</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>8</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0x91 8 25 ED FB 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>帧内原始值 = rad×10000; 只影响打点/显示的 err, 不动驱动; 默认 +0.4613</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x26</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>指令转速斜坡</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>rpm/s</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>300</v>
+      </c>
+      <c r="F18" t="n">
+        <v>300</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2C</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0x91 8 26 01 2C 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>越大起得越快、电流冲击越大</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x26</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>指令转速斜坡</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>rpm/s</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>600</v>
+      </c>
+      <c r="F19" t="n">
+        <v>600</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0x91 8 26 02 58 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>越大起得越快、电流冲击越大</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x26</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>指令转速斜坡</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>rpm/s</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>8</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>B0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>0x91 8 26 04 B0 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>越大起得越快、电流冲击越大</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x27</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>观测器滞后补偿带宽</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>400</v>
+      </c>
+      <c r="F21" t="n">
+        <v>400</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>8</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0x91 8 27 01 90 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>θ_true-θ_est ≈ atan(|we|/(α·fs+w)); 默认 400, 按实测残差微调</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x27</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>观测器滞后补偿带宽</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>800</v>
+      </c>
+      <c r="F22" t="n">
+        <v>800</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>8</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>0x91 8 27 03 20 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>θ_true-θ_est ≈ atan(|we|/(α·fs+w)); 默认 400, 按实测残差微调</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0x27</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>观测器滞后补偿带宽</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>rad/s</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>D0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>0x91 8 27 07 D0 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>θ_true-θ_est ≈ atan(|we|/(α·fs+w)); 默认 400, 按实测残差微调</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x28</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>驱动角来源</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>0x91 8 28 00 00 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>0=开环积分角(不需要编码器, 默认) 1=编码器电角度+转矩角</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x28</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>驱动角来源</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>8</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>0x91 8 28 00 01 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>0=开环积分角(不需要编码器, 默认) 1=编码器电角度+转矩角</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>起步对齐电压</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>0x91 8 29 E3 60 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>原始值 = V×1000; 使能后先在固定角停 300ms 把转子拉到位; 0=不对齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x29</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>起步对齐电压</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>0x91 8 29 00 00 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>原始值 = V×1000; 使能后先在固定角停 300ms 把转子拉到位; 0=不对齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>低频强制启动电压</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2800</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2800000</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>8</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>0x91 8 2A B9 80 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>★解决起步堵转: fe&lt;fres 或还没牵入时电压不低于此值; 原始值 = V×1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>低频强制启动电压</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>0x91 8 2A 09 00 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>★解决起步堵转: fe&lt;fres 或还没牵入时电压不低于此值; 原始值 = V×1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x2A</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>低频强制启动电压</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>8</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>0x91 8 2A AA 20 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>★解决起步堵转: fe&lt;fres 或还没牵入时电压不低于此值; 原始值 = V×1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x2B</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>低频强制段上界频率</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>600</v>
+      </c>
+      <c r="F31" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>8</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>EA</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>0x91 8 2B EA 60 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>原始值 = Hz×100; 默认 600=6Hz; 起步无力就提到 8~10Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x2B</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>低频强制段上界频率</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>900</v>
+      </c>
+      <c r="F32" t="n">
+        <v>90000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>5F</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>0x91 8 2B 5F 90 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>原始值 = Hz×100; 默认 600=6Hz; 起步无力就提到 8~10Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x2B</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>低频强制段上界频率</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F33" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>C0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>0x91 8 2B D4 C0 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>原始值 = Hz×100; 默认 600=6Hz; 起步无力就提到 8~10Hz</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x30</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SMO 打点流开关</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>0x91 8 30 00 01 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1=开始 1kHz USB CSV 打点; 0=停止</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SMO 打点流开关</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0x91</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>0x91 8 30 00 00 00 00 00 00 00</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1=开始 1kHz USB CSV 打点; 0=停止</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:R35"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>命令</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>vf &lt;rpm&gt;</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>进入开环并把目标转速设为 rpm(电机侧), 例: vf 1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>vf</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>只进入开环, 不改目标转速</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>退出开环, 三相占空比封零</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cur &lt;A&gt;</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>回到闭环电流模式, iq = A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>spd &lt;rpm&gt;</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>回到闭环速度模式</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>slope &lt;V/Hz&gt;</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>改 V/F 斜率, 例: slope 0.055</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>vboost &lt;V&gt;</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>改低速补偿电压, 例: vboost 1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>vmax &lt;V&gt;</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>改电压上限, 例: vmax 6.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ramp &lt;rpm/s&gt;</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>改指令转速斜坡</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fstart &lt;Hz&gt;</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>改开环积分角的起始电频率(默认 0.5Hz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>valign &lt;V&gt;</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>改起步对齐电压(默认 1.5V, 0=不对齐)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>vlo &lt;V&gt;</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>★改低频强制启动电压(默认 2.8V): 起步堵转就加到 3.5~4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fres &lt;Hz&gt;</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>改低频强制段上界频率(默认 6Hz): 起步无力提到 8~10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>drv &lt;0|1&gt;</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>驱动角来源: 0=开环积分角(无编码器, 默认) 1=编码器角</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>angle &lt;rad&gt;</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>改编码器模式下的转矩角, 例: angle 1.5708</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>off &lt;rad&gt;</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>改观测角对照偏置(只影响打点显示), 例: off 0.4613</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>lag &lt;rad/s&gt;</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>改滞后补偿等效带宽(默认 400), 用来压随转速漂的残差</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>gain &lt;V&gt;</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>改滑模增益 k(默认 50V)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delta &lt;A&gt;</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>改边界层 δ(默认 8A, 改小要重新核算稳定性)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>stream &lt;0|1&gt;</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>打点流开关</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>打印状态(含 TIM1 寄存器自检、观测器、V/F 参数、方向自检 smo_dir)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>打印命令列表</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>